--- a/input_data/input_data_complete.xlsx
+++ b/input_data/input_data_complete.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2196D9-14DE-4BCF-B7A3-78DDD9B36B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBDD35B-D2FB-4EFE-837E-62DBC33BA7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="12" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -27,20 +27,21 @@
     <sheet name="cf" sheetId="7" r:id="rId12"/>
     <sheet name="inflow" sheetId="3" r:id="rId13"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId14"/>
-    <sheet name="price" sheetId="4" r:id="rId15"/>
-    <sheet name="markets" sheetId="5" r:id="rId16"/>
-    <sheet name="bid_slots" sheetId="27" r:id="rId17"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId21"/>
-    <sheet name="risk" sheetId="17" r:id="rId22"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId23"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId24"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId25"/>
-    <sheet name="constraints" sheetId="14" r:id="rId26"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId27"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="29" r:id="rId15"/>
+    <sheet name="price" sheetId="4" r:id="rId16"/>
+    <sheet name="markets" sheetId="5" r:id="rId17"/>
+    <sheet name="bid_slots" sheetId="27" r:id="rId18"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId19"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId22"/>
+    <sheet name="risk" sheetId="17" r:id="rId23"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
+    <sheet name="constraints" sheetId="14" r:id="rId27"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="187">
   <si>
     <t>node</t>
   </si>
@@ -606,6 +607,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -658,12 +674,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -686,9 +699,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -726,7 +739,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -832,7 +845,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -974,7 +987,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -983,169 +996,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>44671.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>44671.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1156,27 +1169,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -1190,8 +1203,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -1205,8 +1218,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -1220,8 +1233,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -1235,8 +1248,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -1250,116 +1263,116 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1374,17 +1387,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1401,35 +1414,35 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="C2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -1437,8 +1450,8 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -1446,8 +1459,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -1455,8 +1468,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -1464,116 +1477,116 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1588,55 +1601,55 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="4" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -1678,8 +1691,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -1722,8 +1735,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -1766,8 +1779,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -1816,8 +1829,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -1866,116 +1879,116 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1990,13 +2003,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -2013,11 +2026,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>44671</v>
       </c>
       <c r="C2">
@@ -2030,11 +2043,11 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>44671.041666666664</v>
       </c>
       <c r="C3">
@@ -2047,11 +2060,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>44671.08333321759</v>
       </c>
       <c r="C4">
@@ -2064,54 +2077,54 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2121,178 +2134,31 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35200F8-1080-4CAC-B6CC-9D499CBB7C6A}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.125</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666666664</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2302,121 +2168,178 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2426,448 +2349,354 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4988C-98DA-4698-A995-256723868876}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2">
-        <v>45</v>
-      </c>
-      <c r="C2">
-        <v>45</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3">
-        <v>58</v>
-      </c>
-      <c r="C3">
-        <v>58</v>
-      </c>
-      <c r="D3">
-        <v>62</v>
-      </c>
-      <c r="E3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4">
-        <v>55</v>
-      </c>
-      <c r="C4">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D4">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E4">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.125</v>
-      </c>
-      <c r="B5">
-        <v>45</v>
-      </c>
-      <c r="C5">
-        <v>45</v>
-      </c>
-      <c r="D5">
-        <v>55</v>
-      </c>
-      <c r="E5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666666664</v>
-      </c>
-      <c r="B6">
-        <v>75</v>
-      </c>
-      <c r="C6">
-        <v>75</v>
-      </c>
-      <c r="D6">
-        <v>80</v>
-      </c>
-      <c r="E6">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+      <c r="H1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4988C-98DA-4698-A995-256723868876}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="B1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <v>0.27</v>
+        <v>58</v>
       </c>
       <c r="C3">
-        <v>0.27</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+        <v>62</v>
+      </c>
+      <c r="E3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <v>0.27</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>0.28999999999999998</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+        <v>88</v>
+      </c>
+      <c r="E4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <v>0.27</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>0.27</v>
+        <v>75</v>
       </c>
       <c r="D6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -2880,270 +2709,212 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <v>48</v>
+        <v>0.27</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>0.27</v>
       </c>
       <c r="D2">
-        <v>48</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>0.27</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>0.27</v>
       </c>
       <c r="D3">
-        <v>60</v>
-      </c>
-      <c r="E3">
-        <v>56</v>
-      </c>
-      <c r="F3">
-        <v>56</v>
-      </c>
-      <c r="G3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <v>58</v>
+        <v>0.27</v>
       </c>
       <c r="C4">
-        <v>87</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D4">
-        <v>89</v>
-      </c>
-      <c r="E4">
-        <v>44</v>
-      </c>
-      <c r="F4">
-        <v>52.8</v>
-      </c>
-      <c r="G4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>0.27</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>0.27</v>
       </c>
       <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <v>76</v>
+        <v>0.27</v>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>0.27</v>
       </c>
       <c r="D6">
-        <v>76</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3158,21 +2929,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82624B08-6930-4D2B-BCBB-C78CE759E704}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -3180,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -3188,7 +2959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -3196,7 +2967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -3204,7 +2975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3212,7 +2983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3220,7 +2991,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -3228,7 +2999,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>180</v>
       </c>
@@ -3236,7 +3007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>181</v>
       </c>
@@ -3244,7 +3015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -3259,298 +3030,270 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <f>1.1*market_prices!B2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="C2">
-        <f>1.1*market_prices!C2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <f>1.1*market_prices!C2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="E2">
-        <f>0.9*market_prices!B2</f>
-        <v>43.2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <f>0.9*market_prices!C2</f>
-        <v>43.2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <f>0.9*market_prices!C2</f>
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <f>1.1*market_prices!B3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <f>1.1*market_prices!C3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <f>1.1*market_prices!C3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <f>0.9*market_prices!B3</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <f>0.9*market_prices!C3</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <f>0.9*market_prices!C3</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <f>1.1*market_prices!B4</f>
-        <v>63.800000000000004</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <f>1.1*market_prices!C4</f>
-        <v>95.7</v>
+        <v>87</v>
       </c>
       <c r="D4">
-        <f>1.1*market_prices!C4</f>
-        <v>95.7</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <f>0.9*market_prices!B4</f>
-        <v>52.2</v>
+        <v>44</v>
       </c>
       <c r="F4">
-        <f>0.9*market_prices!C4</f>
-        <v>78.3</v>
+        <v>52.8</v>
       </c>
       <c r="G4">
-        <f>0.9*market_prices!C4</f>
-        <v>78.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <f>1.1*market_prices!B5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <f>1.1*market_prices!C5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <f>1.1*market_prices!C5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <f>0.9*market_prices!B5</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <f>0.9*market_prices!C5</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <f>0.9*market_prices!C5</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <f>1.1*market_prices!B6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="C6">
-        <f>1.1*market_prices!C6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="D6">
-        <f>1.1*market_prices!C6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <f>0.9*market_prices!B6</f>
-        <v>68.400000000000006</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <f>0.9*market_prices!C6</f>
-        <v>68.400000000000006</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <f>0.9*market_prices!C6</f>
-        <v>68.400000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3563,24 +3306,328 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="6" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
+        <f>1.1*market_prices!B2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="C2">
+        <f>1.1*market_prices!C2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="D2">
+        <f>1.1*market_prices!C2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="E2">
+        <f>0.9*market_prices!B2</f>
+        <v>43.2</v>
+      </c>
+      <c r="F2">
+        <f>0.9*market_prices!C2</f>
+        <v>43.2</v>
+      </c>
+      <c r="G2">
+        <f>0.9*market_prices!C2</f>
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <f>1.1*market_prices!B3</f>
+        <v>66</v>
+      </c>
+      <c r="C3">
+        <f>1.1*market_prices!C3</f>
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <f>1.1*market_prices!C3</f>
+        <v>66</v>
+      </c>
+      <c r="E3">
+        <f>0.9*market_prices!B3</f>
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <f>0.9*market_prices!C3</f>
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <f>0.9*market_prices!C3</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <f>1.1*market_prices!B4</f>
+        <v>63.800000000000004</v>
+      </c>
+      <c r="C4">
+        <f>1.1*market_prices!C4</f>
+        <v>95.7</v>
+      </c>
+      <c r="D4">
+        <f>1.1*market_prices!C4</f>
+        <v>95.7</v>
+      </c>
+      <c r="E4">
+        <f>0.9*market_prices!B4</f>
+        <v>52.2</v>
+      </c>
+      <c r="F4">
+        <f>0.9*market_prices!C4</f>
+        <v>78.3</v>
+      </c>
+      <c r="G4">
+        <f>0.9*market_prices!C4</f>
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+      <c r="B5">
+        <f>1.1*market_prices!B5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="C5">
+        <f>1.1*market_prices!C5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="D5">
+        <f>1.1*market_prices!C5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="E5">
+        <f>0.9*market_prices!B5</f>
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <f>0.9*market_prices!C5</f>
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <f>0.9*market_prices!C5</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
+      <c r="B6">
+        <f>1.1*market_prices!B6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="C6">
+        <f>1.1*market_prices!C6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="D6">
+        <f>1.1*market_prices!C6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="E6">
+        <f>0.9*market_prices!B6</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="F6">
+        <f>0.9*market_prices!C6</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="G6">
+        <f>0.9*market_prices!C6</f>
+        <v>68.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505F64D8-0D97-4D94-B3D0-5B7D8B3D4E80}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E1"/>
@@ -3623,8 +3670,8 @@
       <c r="AP1"/>
       <c r="AQ1"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -3638,8 +3685,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -3653,8 +3700,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -3668,8 +3715,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -3683,8 +3730,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -3698,116 +3745,116 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3819,23 +3866,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -3843,55 +3890,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>87</v>
       </c>
       <c r="B3">
         <v>0.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4">
-        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -3901,167 +3905,40 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.125</v>
-      </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666666664</v>
-      </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -4071,29 +3948,192 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4107,8 +4147,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4122,8 +4162,8 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4137,8 +4177,8 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -4152,8 +4192,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -4167,116 +4207,116 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4288,20 +4328,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="12" max="21" width="3.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="12" max="21" width="3.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -4315,7 +4355,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -4329,7 +4369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -4343,7 +4383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -4357,17 +4397,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F26" s="6"/>
-    </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="3"/>
+    </row>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4375,22 +4415,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="2" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -4439,8 +4479,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4490,8 +4530,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4541,8 +4581,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4592,8 +4632,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -4643,8 +4683,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -4694,116 +4734,116 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4815,16 +4855,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -4837,8 +4877,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4852,8 +4892,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4867,8 +4907,8 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4882,8 +4922,8 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
@@ -4897,8 +4937,8 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
@@ -4912,116 +4952,116 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -5036,517 +5076,517 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
         <v>4</v>
       </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
         <v>393.15</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="2">
         <v>330.15</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="2">
         <v>20</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="2">
         <v>20</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="2">
         <v>373.15</v>
       </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5">
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
         <f>1.16388888888889/5</f>
         <v>0.23277777777777803</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>136</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
         <v>300.14999999999998</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="2">
         <v>253.15</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="2">
         <v>100000000</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="2">
         <v>100000000</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="2">
         <v>273.14999999999998</v>
       </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5">
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
         <v>10000000</v>
       </c>
-      <c r="P8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
         <v>1000</v>
       </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>1000</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="2">
         <v>1000</v>
       </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
         <v>0.9</v>
       </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-      <c r="P10" s="5">
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5559,495 +5599,495 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
         <v>0.9</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="2">
         <v>0.3</v>
       </c>
-      <c r="I2" s="5">
-        <v>1</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
         <v>4</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <v>3</v>
       </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
         <v>3</v>
       </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
         <v>0.7</v>
       </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="2">
         <v>0.99</v>
       </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
         <v>0.99</v>
       </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
         <v>0.99</v>
       </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5">
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6060,20 +6100,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6084,7 +6124,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -6095,7 +6135,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -6106,7 +6146,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -6126,53 +6166,53 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2">
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -6192,7 +6232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -6221,560 +6261,559 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2">
         <v>0.5</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>0.5</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>0.6</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>0.5</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>0.5</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3">
         <v>0.6</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>0.5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>0.5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>0.6</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>0.6</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>15</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>0.5</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>0.5</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>0.6</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7">
         <v>15</v>
       </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>0.6</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.6</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9">
         <v>0.5</v>
       </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>0.6</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9">
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>0.6</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>20</v>
       </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>0.6</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11">
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>20</v>
       </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>0.6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12">
         <v>0.6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>20</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>0.6</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13">
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>20</v>
       </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
         <v>0.6</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14">
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>138</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>20</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
         <v>0.6</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15">
         <v>0.6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <v>1000</v>
       </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16" s="4">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
         <v>0.6</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16">
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>1000</v>
       </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
         <v>0.6</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17">
         <v>0.6</v>
       </c>
     </row>
@@ -6787,16 +6826,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="6" customWidth="1"/>
-    <col min="2" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
@@ -6818,158 +6857,158 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>44671</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>44671</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3">
         <v>44671</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>44671.041666666664</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>44671.041666666664</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>44671.041666666664</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6984,31 +7023,31 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>137</v>
       </c>

--- a/input_data/input_data_complete.xlsx
+++ b/input_data/input_data_complete.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBDD35B-D2FB-4EFE-837E-62DBC33BA7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3158B0A4-B03A-4E1B-8C4C-55D29449A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="188">
   <si>
     <t>node</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -2135,13 +2138,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35200F8-1080-4CAC-B6CC-9D499CBB7C6A}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>182</v>
       </c>
@@ -2159,6 +2162,9 @@
       </c>
       <c r="F1" t="s">
         <v>186</v>
+      </c>
+      <c r="G1" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/input_data/input_data_complete.xlsx
+++ b/input_data/input_data_complete.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3158B0A4-B03A-4E1B-8C4C-55D29449A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6630D23-6963-4AA2-952A-6A0E9411416F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="796" firstSheet="5" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -30,18 +30,19 @@
     <sheet name="flex_inflow" sheetId="29" r:id="rId15"/>
     <sheet name="price" sheetId="4" r:id="rId16"/>
     <sheet name="markets" sheetId="5" r:id="rId17"/>
-    <sheet name="bid_slots" sheetId="27" r:id="rId18"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId19"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId22"/>
-    <sheet name="risk" sheetId="17" r:id="rId23"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
-    <sheet name="constraints" sheetId="14" r:id="rId27"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId29"/>
+    <sheet name="market_limits" sheetId="30" r:id="rId18"/>
+    <sheet name="bid_slots" sheetId="27" r:id="rId19"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId20"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId21"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId22"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId23"/>
+    <sheet name="risk" sheetId="17" r:id="rId24"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId25"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId26"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId27"/>
+    <sheet name="constraints" sheetId="14" r:id="rId28"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId29"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="191">
   <si>
     <t>node</t>
   </si>
@@ -625,6 +626,15 @@
   </si>
   <si>
     <t>deviation_penalty</t>
+  </si>
+  <si>
+    <t>fi1</t>
+  </si>
+  <si>
+    <t>fi2</t>
+  </si>
+  <si>
+    <t>fi3</t>
   </si>
 </sst>
 </file>
@@ -999,168 +1009,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>44671.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>44671.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
   </sheetData>
@@ -1172,12 +1182,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1191,7 +1201,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1206,7 +1216,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1221,7 +1231,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1236,7 +1246,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1251,7 +1261,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1266,115 +1276,115 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1390,9 +1400,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -1400,7 +1410,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1417,14 +1427,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1433,7 +1443,7 @@
       </c>
       <c r="C1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1444,7 +1454,7 @@
       <c r="C2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1453,7 +1463,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1462,7 +1472,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1471,7 +1481,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1480,115 +1490,115 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1604,13 +1614,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-    <col min="4" max="7" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="4" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1651,7 +1661,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1694,7 +1704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1738,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1782,7 +1792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1832,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1882,115 +1892,115 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2006,13 +2016,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -2029,7 +2039,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2046,7 +2056,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2063,7 +2073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2080,50 +2090,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2138,13 +2148,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35200F8-1080-4CAC-B6CC-9D499CBB7C6A}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>182</v>
       </c>
@@ -2165,6 +2175,75 @@
       </c>
       <c r="G1" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>-3</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>-3</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>-3</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2176,12 +2255,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2189,7 +2268,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -2198,7 +2277,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -2207,7 +2286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -2216,7 +2295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -2225,7 +2304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -2234,115 +2313,115 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2357,17 +2436,17 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -2402,7 +2481,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2437,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
@@ -2460,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -2479,229 +2558,211 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4988C-98DA-4698-A995-256723868876}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EBC392-5844-424D-8521-4B577CFE2C0C}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>62</v>
-      </c>
-      <c r="E3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>88</v>
-      </c>
-      <c r="E4">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>55</v>
-      </c>
-      <c r="E5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>80</v>
-      </c>
-      <c r="E6">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2710,216 +2771,233 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4988C-98DA-4698-A995-256723868876}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <v>0.27</v>
+        <v>58</v>
       </c>
       <c r="C3">
-        <v>0.27</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="E3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <v>0.27</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>0.28999999999999998</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="E4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>0.27</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <v>0.27</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>0.27</v>
+        <v>75</v>
       </c>
       <c r="D6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2935,13 +3013,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82624B08-6930-4D2B-BCBB-C78CE759E704}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -2949,7 +3027,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -2957,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -2965,7 +3043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -2973,7 +3051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -2981,7 +3059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -2989,7 +3067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -2997,7 +3075,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -3005,7 +3083,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>180</v>
       </c>
@@ -3013,7 +3091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>181</v>
       </c>
@@ -3021,7 +3099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -3036,269 +3114,211 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="4" width="11.109375" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <v>48</v>
+        <v>0.27</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>0.27</v>
       </c>
       <c r="D2">
-        <v>48</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>0.27</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>0.27</v>
       </c>
       <c r="D3">
-        <v>60</v>
-      </c>
-      <c r="E3">
-        <v>56</v>
-      </c>
-      <c r="F3">
-        <v>56</v>
-      </c>
-      <c r="G3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <v>58</v>
+        <v>0.27</v>
       </c>
       <c r="C4">
-        <v>87</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D4">
-        <v>89</v>
-      </c>
-      <c r="E4">
-        <v>44</v>
-      </c>
-      <c r="F4">
-        <v>52.8</v>
-      </c>
-      <c r="G4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>0.27</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>0.27</v>
       </c>
       <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <v>76</v>
+        <v>0.27</v>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>0.27</v>
       </c>
       <c r="D6">
-        <v>76</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3312,297 +3332,269 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="6" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
       <c r="B2">
-        <f>1.1*market_prices!B2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="C2">
-        <f>1.1*market_prices!C2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <f>1.1*market_prices!C2</f>
-        <v>52.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="E2">
-        <f>0.9*market_prices!B2</f>
-        <v>43.2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <f>0.9*market_prices!C2</f>
-        <v>43.2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <f>0.9*market_prices!C2</f>
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
       <c r="B3">
-        <f>1.1*market_prices!B3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <f>1.1*market_prices!C3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <f>1.1*market_prices!C3</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <f>0.9*market_prices!B3</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <f>0.9*market_prices!C3</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <f>0.9*market_prices!C3</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
       <c r="B4">
-        <f>1.1*market_prices!B4</f>
-        <v>63.800000000000004</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <f>1.1*market_prices!C4</f>
-        <v>95.7</v>
+        <v>87</v>
       </c>
       <c r="D4">
-        <f>1.1*market_prices!C4</f>
-        <v>95.7</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <f>0.9*market_prices!B4</f>
-        <v>52.2</v>
+        <v>44</v>
       </c>
       <c r="F4">
-        <f>0.9*market_prices!C4</f>
-        <v>78.3</v>
+        <v>52.8</v>
       </c>
       <c r="G4">
-        <f>0.9*market_prices!C4</f>
-        <v>78.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
       <c r="B5">
-        <f>1.1*market_prices!B5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <f>1.1*market_prices!C5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <f>1.1*market_prices!C5</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <f>0.9*market_prices!B5</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <f>0.9*market_prices!C5</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <f>0.9*market_prices!C5</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
       <c r="B6">
-        <f>1.1*market_prices!B6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="C6">
-        <f>1.1*market_prices!C6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="D6">
-        <f>1.1*market_prices!C6</f>
-        <v>83.600000000000009</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <f>0.9*market_prices!B6</f>
-        <v>68.400000000000006</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <f>0.9*market_prices!C6</f>
-        <v>68.400000000000006</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <f>0.9*market_prices!C6</f>
-        <v>68.400000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3616,14 +3608,318 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
+        <f>1.1*market_prices!B2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="C2">
+        <f>1.1*market_prices!C2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="D2">
+        <f>1.1*market_prices!C2</f>
+        <v>52.800000000000004</v>
+      </c>
+      <c r="E2">
+        <f>0.9*market_prices!B2</f>
+        <v>43.2</v>
+      </c>
+      <c r="F2">
+        <f>0.9*market_prices!C2</f>
+        <v>43.2</v>
+      </c>
+      <c r="G2">
+        <f>0.9*market_prices!C2</f>
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <f>1.1*market_prices!B3</f>
+        <v>66</v>
+      </c>
+      <c r="C3">
+        <f>1.1*market_prices!C3</f>
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <f>1.1*market_prices!C3</f>
+        <v>66</v>
+      </c>
+      <c r="E3">
+        <f>0.9*market_prices!B3</f>
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <f>0.9*market_prices!C3</f>
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <f>0.9*market_prices!C3</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <f>1.1*market_prices!B4</f>
+        <v>63.800000000000004</v>
+      </c>
+      <c r="C4">
+        <f>1.1*market_prices!C4</f>
+        <v>95.7</v>
+      </c>
+      <c r="D4">
+        <f>1.1*market_prices!C4</f>
+        <v>95.7</v>
+      </c>
+      <c r="E4">
+        <f>0.9*market_prices!B4</f>
+        <v>52.2</v>
+      </c>
+      <c r="F4">
+        <f>0.9*market_prices!C4</f>
+        <v>78.3</v>
+      </c>
+      <c r="G4">
+        <f>0.9*market_prices!C4</f>
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+      <c r="B5">
+        <f>1.1*market_prices!B5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="C5">
+        <f>1.1*market_prices!C5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="D5">
+        <f>1.1*market_prices!C5</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="E5">
+        <f>0.9*market_prices!B5</f>
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <f>0.9*market_prices!C5</f>
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <f>0.9*market_prices!C5</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
+      <c r="B6">
+        <f>1.1*market_prices!B6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="C6">
+        <f>1.1*market_prices!C6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="D6">
+        <f>1.1*market_prices!C6</f>
+        <v>83.600000000000009</v>
+      </c>
+      <c r="E6">
+        <f>0.9*market_prices!B6</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="F6">
+        <f>0.9*market_prices!C6</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="G6">
+        <f>0.9*market_prices!C6</f>
+        <v>68.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505F64D8-0D97-4D94-B3D0-5B7D8B3D4E80}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3676,7 +3972,7 @@
       <c r="AP1"/>
       <c r="AQ1"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -3691,7 +3987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -3706,7 +4002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -3721,7 +4017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -3736,7 +4032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -3751,115 +4047,115 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3872,15 +4168,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -3888,7 +4184,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -3896,55 +4192,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>87</v>
       </c>
       <c r="B3">
         <v>0.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4">
-        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -3954,160 +4207,40 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666666664</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -4117,92 +4250,255 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-      <c r="D3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+      <c r="D3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+      <c r="D4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
       <c r="B6">
         <v>3</v>
       </c>
@@ -4213,115 +4509,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4334,20 +4630,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="12" max="21" width="3.88671875" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="12" max="21" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -4361,7 +4657,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -4375,7 +4671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -4389,7 +4685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -4403,15 +4699,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F26" s="3"/>
     </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
     </row>
@@ -4421,21 +4717,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -4485,7 +4781,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -4536,7 +4832,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4587,7 +4883,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4638,7 +4934,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -4689,7 +4985,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -4740,333 +5036,115 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C3">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="D3">
-        <v>4.28571428571429</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C4">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="D4">
-        <v>4.28571428571429</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.125</v>
-      </c>
-      <c r="B5">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C5">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="D5">
-        <v>4.28571428571429</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666666664</v>
-      </c>
-      <c r="B6">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C6">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="D6">
-        <v>4.28571428571429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="str">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="str">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="str">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="str">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -5082,20 +5160,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5145,7 +5223,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5195,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5245,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5295,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -5345,7 +5423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -5395,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -5446,7 +5524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>136</v>
       </c>
@@ -5496,7 +5574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -5546,7 +5624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -5597,6 +5675,224 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+      <c r="B3">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C3">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="D3">
+        <v>4.28571428571429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+      <c r="B4">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C4">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="D4">
+        <v>4.28571428571429</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.125</v>
+      </c>
+      <c r="B5">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C5">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="D5">
+        <v>4.28571428571429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666666664</v>
+      </c>
+      <c r="B6">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C6">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="D6">
+        <v>4.28571428571429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="str">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="str">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="str">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="str">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5605,22 +5901,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -5673,7 +5969,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -5726,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -5779,7 +6075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -5832,7 +6128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -5885,7 +6181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -5938,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -5991,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -6044,7 +6340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -6106,9 +6402,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
@@ -6119,7 +6415,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6130,7 +6426,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -6141,7 +6437,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -6152,7 +6448,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -6172,9 +6468,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -6218,7 +6514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -6238,7 +6534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -6267,19 +6563,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -6311,7 +6607,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -6343,7 +6639,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -6375,7 +6671,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -6407,7 +6703,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -6439,7 +6735,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6471,7 +6767,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -6503,7 +6799,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -6535,7 +6831,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -6567,7 +6863,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -6599,7 +6895,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -6631,7 +6927,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -6663,7 +6959,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -6695,7 +6991,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -6727,7 +7023,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -6759,7 +7055,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -6791,7 +7087,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -6832,15 +7128,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -6863,7 +7159,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6886,7 +7182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6909,112 +7205,112 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7029,14 +7325,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
@@ -7053,7 +7349,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>

--- a/input_data/input_data_complete.xlsx
+++ b/input_data/input_data_complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6630D23-6963-4AA2-952A-6A0E9411416F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BD3620-6732-4F9D-A80F-D6B8622C168B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="796" firstSheet="5" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="796" firstSheet="16" activeTab="17" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="197">
   <si>
     <t>node</t>
   </si>
@@ -635,6 +635,24 @@
   </si>
   <si>
     <t>fi3</t>
+  </si>
+  <si>
+    <t>fcr_up,up,s1</t>
+  </si>
+  <si>
+    <t>fcr_up,up,s2</t>
+  </si>
+  <si>
+    <t>fcr_up,up,s3</t>
+  </si>
+  <si>
+    <t>fcr_up,dw,s1</t>
+  </si>
+  <si>
+    <t>fcr_up,dw,s2</t>
+  </si>
+  <si>
+    <t>fcr_up,dw,s3</t>
   </si>
 </sst>
 </file>
@@ -1009,168 +1027,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>44671.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>44671.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
   </sheetData>
@@ -1182,12 +1200,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1201,7 +1219,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1216,7 +1234,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1231,7 +1249,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1246,7 +1264,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1261,7 +1279,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1276,115 +1294,115 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1400,9 +1418,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -1410,7 +1428,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1427,14 +1445,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1443,7 +1461,7 @@
       </c>
       <c r="C1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1454,7 +1472,7 @@
       <c r="C2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1463,7 +1481,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1472,7 +1490,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1481,7 +1499,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1490,115 +1508,115 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -1614,13 +1632,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
-    <col min="4" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1661,7 +1679,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -1704,7 +1722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -1748,7 +1766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -1792,7 +1810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -1842,7 +1860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -1892,115 +1910,115 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2016,13 +2034,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -2039,7 +2057,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2073,7 +2091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2090,50 +2108,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2149,12 +2167,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35200F8-1080-4CAC-B6CC-9D499CBB7C6A}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>182</v>
       </c>
@@ -2177,7 +2195,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -2200,7 +2218,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2223,7 +2241,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2255,12 +2273,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2268,7 +2286,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -2277,7 +2295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -2286,7 +2304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -2295,7 +2313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -2304,7 +2322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -2313,115 +2331,115 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2436,17 +2454,17 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -2481,7 +2499,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2516,7 +2534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
@@ -2559,27 +2577,36 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EBC392-5844-424D-8521-4B577CFE2C0C}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="E1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -2593,8 +2620,17 @@
       <c r="D2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -2608,8 +2644,17 @@
       <c r="D3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -2623,8 +2668,17 @@
       <c r="D4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -2638,8 +2692,17 @@
       <c r="D5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -2653,116 +2716,125 @@
       <c r="D6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -2777,12 +2849,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4988C-98DA-4698-A995-256723868876}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2799,7 +2871,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -2817,7 +2889,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -2835,7 +2907,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -2853,7 +2925,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -2871,7 +2943,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -2889,115 +2961,115 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3013,13 +3085,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82624B08-6930-4D2B-BCBB-C78CE759E704}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -3027,7 +3099,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -3035,7 +3107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -3043,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -3051,7 +3123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -3059,7 +3131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3067,7 +3139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3075,7 +3147,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -3083,7 +3155,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>180</v>
       </c>
@@ -3091,7 +3163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>181</v>
       </c>
@@ -3099,7 +3171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -3116,12 +3188,12 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3135,7 +3207,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -3150,7 +3222,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -3165,7 +3237,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -3180,7 +3252,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -3195,7 +3267,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -3210,115 +3282,115 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3334,16 +3406,16 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3366,7 +3438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -3390,7 +3462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -3414,7 +3486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -3438,7 +3510,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -3462,7 +3534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -3486,115 +3558,115 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3610,14 +3682,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="6" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3640,7 +3712,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -3670,7 +3742,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -3700,7 +3772,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -3730,7 +3802,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -3760,7 +3832,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -3790,115 +3862,115 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -3914,12 +3986,12 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505F64D8-0D97-4D94-B3D0-5B7D8B3D4E80}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3972,7 +4044,7 @@
       <c r="AP1"/>
       <c r="AQ1"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -3987,7 +4059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4002,7 +4074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4017,7 +4089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -4032,7 +4104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -4047,115 +4119,115 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4171,12 +4243,12 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -4184,7 +4256,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -4192,7 +4264,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -4209,9 +4281,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -4219,7 +4291,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -4227,7 +4299,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -4235,7 +4307,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -4252,155 +4324,155 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4415,12 +4487,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -4434,7 +4506,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -4449,7 +4521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4464,7 +4536,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4479,7 +4551,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -4494,7 +4566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -4509,115 +4581,115 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4633,17 +4705,17 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="12" max="21" width="3.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="12" max="21" width="3.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -4657,7 +4729,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -4671,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -4685,7 +4757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -4699,15 +4771,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F26" s="3"/>
     </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
     </row>
@@ -4720,18 +4792,18 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -4781,7 +4853,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -4832,7 +4904,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4883,7 +4955,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4934,7 +5006,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -4985,7 +5057,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -5036,115 +5108,115 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -5160,20 +5232,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5223,7 +5295,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5273,7 +5345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5323,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5373,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -5423,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -5473,7 +5545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -5524,7 +5596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>136</v>
       </c>
@@ -5574,7 +5646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -5624,7 +5696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -5683,12 +5755,12 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -5702,7 +5774,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -5717,7 +5789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -5732,7 +5804,7 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -5747,7 +5819,7 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.125</v>
@@ -5762,7 +5834,7 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666666664</v>
@@ -5777,115 +5849,115 @@
         <v>4.28571428571429</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -5901,22 +5973,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -5969,7 +6041,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -6022,7 +6094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -6075,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6128,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -6181,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -6234,7 +6306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -6287,7 +6359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -6340,7 +6412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -6402,9 +6474,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
@@ -6415,7 +6487,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6426,7 +6498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -6437,7 +6509,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -6448,7 +6520,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -6468,9 +6540,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -6514,7 +6586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -6534,7 +6606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -6563,19 +6635,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -6607,7 +6679,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -6639,7 +6711,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -6671,7 +6743,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -6703,7 +6775,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -6735,7 +6807,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6767,7 +6839,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -6799,7 +6871,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -6831,7 +6903,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -6863,7 +6935,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -6895,7 +6967,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -6927,7 +6999,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -6959,7 +7031,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -6991,7 +7063,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -7023,7 +7095,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -7055,7 +7127,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -7087,7 +7159,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -7128,15 +7200,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -7159,7 +7231,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7182,7 +7254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7205,112 +7277,112 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7325,14 +7397,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
@@ -7349,7 +7421,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>137</v>
       </c>
